--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/NEBRASKA_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/NEBRASKA_2021.xlsx
@@ -1327,7 +1327,7 @@
         <v>4</v>
       </c>
       <c r="D54">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="55">
@@ -1669,7 +1669,7 @@
         <v>4</v>
       </c>
       <c r="D73">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="74">
@@ -1813,7 +1813,7 @@
         <v>4</v>
       </c>
       <c r="D81">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="82">
@@ -2047,7 +2047,7 @@
         <v>4</v>
       </c>
       <c r="D94">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="95">
@@ -2119,7 +2119,7 @@
         <v>4</v>
       </c>
       <c r="D98">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="99">
@@ -2623,7 +2623,7 @@
         <v>4</v>
       </c>
       <c r="D126">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="127">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C127">
@@ -2749,7 +2749,7 @@
         <v>4</v>
       </c>
       <c r="D133">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="134">
@@ -2785,7 +2785,7 @@
         <v>4</v>
       </c>
       <c r="D135">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="136">
@@ -2929,7 +2929,7 @@
         <v>4</v>
       </c>
       <c r="D143">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="144">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C197">
@@ -3973,7 +3973,7 @@
         <v>4</v>
       </c>
       <c r="D201">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="202">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C204">
@@ -4837,7 +4837,7 @@
         <v>4</v>
       </c>
       <c r="D249">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="250">
@@ -4999,7 +4999,7 @@
         <v>4</v>
       </c>
       <c r="D258">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="259">
@@ -5053,7 +5053,7 @@
         <v>4</v>
       </c>
       <c r="D261">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="262">
@@ -5431,7 +5431,7 @@
         <v>4</v>
       </c>
       <c r="D282">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="283">
@@ -6115,7 +6115,7 @@
         <v>40</v>
       </c>
       <c r="D320">
-        <v>0.009643201542912247</v>
+        <v>0.009643201542912249</v>
       </c>
     </row>
     <row r="321">
@@ -6295,7 +6295,7 @@
         <v>4</v>
       </c>
       <c r="D330">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="331">
@@ -6367,7 +6367,7 @@
         <v>4</v>
       </c>
       <c r="D334">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="335">
@@ -6385,7 +6385,7 @@
         <v>4</v>
       </c>
       <c r="D335">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="336">
@@ -6457,7 +6457,7 @@
         <v>4</v>
       </c>
       <c r="D339">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="340">
@@ -6493,7 +6493,7 @@
         <v>4</v>
       </c>
       <c r="D341">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="342">
@@ -6529,7 +6529,7 @@
         <v>4</v>
       </c>
       <c r="D343">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="344">
@@ -7213,7 +7213,7 @@
         <v>4</v>
       </c>
       <c r="D381">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="382">
@@ -7663,7 +7663,7 @@
         <v>4</v>
       </c>
       <c r="D406">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="407">
@@ -7681,7 +7681,7 @@
         <v>4</v>
       </c>
       <c r="D407">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="408">
@@ -8311,7 +8311,7 @@
         <v>4</v>
       </c>
       <c r="D442">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="443">
@@ -8419,7 +8419,7 @@
         <v>4</v>
       </c>
       <c r="D448">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="449">
@@ -8617,7 +8617,7 @@
         <v>4</v>
       </c>
       <c r="D459">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="460">
@@ -8869,7 +8869,7 @@
         <v>4</v>
       </c>
       <c r="D473">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="474">
@@ -9535,7 +9535,7 @@
         <v>4</v>
       </c>
       <c r="D510">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="511">
@@ -9661,7 +9661,7 @@
         <v>4</v>
       </c>
       <c r="D517">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="518">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C546">
@@ -10237,7 +10237,7 @@
         <v>4</v>
       </c>
       <c r="D549">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="550">
@@ -10975,7 +10975,7 @@
         <v>4</v>
       </c>
       <c r="D590">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="591">
@@ -11335,7 +11335,7 @@
         <v>4</v>
       </c>
       <c r="D610">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="611">
@@ -11803,7 +11803,7 @@
         <v>4</v>
       </c>
       <c r="D636">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="637">
@@ -11875,7 +11875,7 @@
         <v>4</v>
       </c>
       <c r="D640">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="641">
@@ -12469,7 +12469,7 @@
         <v>40</v>
       </c>
       <c r="D673">
-        <v>0.009643201542912247</v>
+        <v>0.009643201542912249</v>
       </c>
     </row>
     <row r="674">
@@ -13099,7 +13099,7 @@
         <v>4</v>
       </c>
       <c r="D708">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="709">
@@ -13117,7 +13117,7 @@
         <v>4</v>
       </c>
       <c r="D709">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="710">
@@ -13153,7 +13153,7 @@
         <v>4</v>
       </c>
       <c r="D711">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="712">
@@ -13657,7 +13657,7 @@
         <v>4</v>
       </c>
       <c r="D739">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="740">
@@ -14143,7 +14143,7 @@
         <v>4</v>
       </c>
       <c r="D766">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="767">
@@ -14161,7 +14161,7 @@
         <v>4</v>
       </c>
       <c r="D767">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="768">
@@ -14521,7 +14521,7 @@
         <v>4</v>
       </c>
       <c r="D787">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="788">
@@ -14557,7 +14557,7 @@
         <v>4</v>
       </c>
       <c r="D789">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="790">
@@ -14665,7 +14665,7 @@
         <v>4</v>
       </c>
       <c r="D795">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="796">
@@ -14719,7 +14719,7 @@
         <v>4</v>
       </c>
       <c r="D798">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="799">
@@ -14737,7 +14737,7 @@
         <v>4</v>
       </c>
       <c r="D799">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="800">
@@ -14863,7 +14863,7 @@
         <v>4</v>
       </c>
       <c r="D806">
-        <v>0.0009643201542912247</v>
+        <v>0.0009643201542912248</v>
       </c>
     </row>
     <row r="807">
